--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117942314</v>
+        <v>117942027</v>
       </c>
       <c r="B5" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1027,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479741</v>
+        <v>479728</v>
       </c>
       <c r="R5" t="n">
-        <v>6953389</v>
+        <v>6953486</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117942027</v>
+        <v>117942314</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,42 +1144,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479728</v>
+        <v>479741</v>
       </c>
       <c r="R6" t="n">
-        <v>6953486</v>
+        <v>6953389</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,12 +1228,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117939984</v>
+        <v>117942062</v>
       </c>
       <c r="B11" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,34 +1709,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479815</v>
+        <v>479773</v>
       </c>
       <c r="R11" t="n">
-        <v>6953640</v>
+        <v>6953376</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117942062</v>
+        <v>117939984</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479773</v>
+        <v>479815</v>
       </c>
       <c r="R12" t="n">
-        <v>6953376</v>
+        <v>6953640</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117943232</v>
+        <v>117938085</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,37 +1933,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479604</v>
+        <v>479712</v>
       </c>
       <c r="R13" t="n">
-        <v>6953667</v>
+        <v>6953704</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,22 +2017,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117938085</v>
+        <v>117943232</v>
       </c>
       <c r="B14" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,37 +2045,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479712</v>
+        <v>479604</v>
       </c>
       <c r="R14" t="n">
-        <v>6953704</v>
+        <v>6953667</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,22 +2129,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117941008</v>
+        <v>117942960</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,34 +2157,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479958</v>
+        <v>479556</v>
       </c>
       <c r="R15" t="n">
-        <v>6953321</v>
+        <v>6953566</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117942960</v>
+        <v>117941137</v>
       </c>
       <c r="B16" t="n">
-        <v>79561</v>
+        <v>78217</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479556</v>
+        <v>479903</v>
       </c>
       <c r="R16" t="n">
-        <v>6953566</v>
+        <v>6953255</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,19 +2353,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117941137</v>
+        <v>117938894</v>
       </c>
       <c r="B17" t="n">
         <v>78217</v>
@@ -2401,17 +2401,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479903</v>
+        <v>479776</v>
       </c>
       <c r="R17" t="n">
-        <v>6953255</v>
+        <v>6953614</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2465,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117938894</v>
+        <v>117941008</v>
       </c>
       <c r="B18" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479776</v>
+        <v>479958</v>
       </c>
       <c r="R18" t="n">
-        <v>6953614</v>
+        <v>6953321</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117941078</v>
+        <v>117936812</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>90648</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479904</v>
+        <v>479671</v>
       </c>
       <c r="R2" t="n">
-        <v>6953265</v>
+        <v>6953744</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117941941</v>
+        <v>117942713</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479761</v>
+        <v>479700</v>
       </c>
       <c r="R3" t="n">
-        <v>6953483</v>
+        <v>6953611</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117941433</v>
+        <v>117938179</v>
       </c>
       <c r="B4" t="n">
-        <v>79589</v>
+        <v>78125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479796</v>
+        <v>479749</v>
       </c>
       <c r="R4" t="n">
-        <v>6953252</v>
+        <v>6953702</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117942027</v>
+        <v>117938085</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,42 +1027,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479728</v>
+        <v>479712</v>
       </c>
       <c r="R5" t="n">
-        <v>6953486</v>
+        <v>6953704</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117942314</v>
+        <v>117942064</v>
       </c>
       <c r="B6" t="n">
-        <v>90517</v>
+        <v>97857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479741</v>
+        <v>479735</v>
       </c>
       <c r="R6" t="n">
-        <v>6953389</v>
+        <v>6953521</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,19 +1223,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117938218</v>
+        <v>117937581</v>
       </c>
       <c r="B7" t="n">
         <v>78217</v>
@@ -1280,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479757</v>
+        <v>479671</v>
       </c>
       <c r="R7" t="n">
-        <v>6953691</v>
+        <v>6953726</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117940275</v>
+        <v>117941433</v>
       </c>
       <c r="B8" t="n">
-        <v>79069</v>
+        <v>79589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,38 +1359,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479803</v>
+        <v>479796</v>
       </c>
       <c r="R8" t="n">
-        <v>6953633</v>
+        <v>6953252</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1464,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117940785</v>
+        <v>117936521</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>78217</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,42 +1475,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479909</v>
+        <v>479658</v>
       </c>
       <c r="R9" t="n">
-        <v>6953394</v>
+        <v>6953757</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117937924</v>
+        <v>117941709</v>
       </c>
       <c r="B10" t="n">
-        <v>96791</v>
+        <v>56499</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1587,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479739</v>
+        <v>479783</v>
       </c>
       <c r="R10" t="n">
-        <v>6953704</v>
+        <v>6953379</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1693,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117942062</v>
+        <v>117937050</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>56499</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,38 +1700,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479773</v>
+        <v>479672</v>
       </c>
       <c r="R11" t="n">
-        <v>6953376</v>
+        <v>6953743</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117939984</v>
+        <v>117941840</v>
       </c>
       <c r="B12" t="n">
-        <v>78217</v>
+        <v>5480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,37 +1821,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479815</v>
+        <v>479804</v>
       </c>
       <c r="R12" t="n">
-        <v>6953640</v>
+        <v>6953380</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,22 +1905,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117938085</v>
+        <v>117937924</v>
       </c>
       <c r="B13" t="n">
-        <v>79561</v>
+        <v>96791</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479712</v>
+        <v>479739</v>
       </c>
       <c r="R13" t="n">
         <v>6953704</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,22 +2017,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117943232</v>
+        <v>117942027</v>
       </c>
       <c r="B14" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,34 +2045,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479604</v>
+        <v>479728</v>
       </c>
       <c r="R14" t="n">
-        <v>6953667</v>
+        <v>6953486</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2141,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117942960</v>
+        <v>117940586</v>
       </c>
       <c r="B15" t="n">
-        <v>79561</v>
+        <v>79098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,37 +2162,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479556</v>
+        <v>479857</v>
       </c>
       <c r="R15" t="n">
-        <v>6953566</v>
+        <v>6953493</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,22 +2246,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117941137</v>
+        <v>117938245</v>
       </c>
       <c r="B16" t="n">
-        <v>78217</v>
+        <v>78216</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,37 +2274,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479903</v>
+        <v>479770</v>
       </c>
       <c r="R16" t="n">
-        <v>6953255</v>
+        <v>6953643</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,22 +2358,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117938894</v>
+        <v>117942960</v>
       </c>
       <c r="B17" t="n">
-        <v>78217</v>
+        <v>79561</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,34 +2386,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479776</v>
+        <v>479556</v>
       </c>
       <c r="R17" t="n">
-        <v>6953614</v>
+        <v>6953566</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2477,7 +2482,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117941008</v>
+        <v>117942062</v>
       </c>
       <c r="B18" t="n">
         <v>78480</v>
@@ -2513,17 +2518,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479958</v>
+        <v>479773</v>
       </c>
       <c r="R18" t="n">
-        <v>6953321</v>
+        <v>6953376</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2552,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,22 +2582,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117938179</v>
+        <v>117941941</v>
       </c>
       <c r="B19" t="n">
-        <v>78125</v>
+        <v>78480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,34 +2610,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479749</v>
+        <v>479761</v>
       </c>
       <c r="R19" t="n">
-        <v>6953702</v>
+        <v>6953483</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2701,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117942064</v>
+        <v>117943232</v>
       </c>
       <c r="B20" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,25 +2718,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479735</v>
+        <v>479604</v>
       </c>
       <c r="R20" t="n">
-        <v>6953521</v>
+        <v>6953667</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2813,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117938245</v>
+        <v>117939942</v>
       </c>
       <c r="B21" t="n">
-        <v>78216</v>
+        <v>79069</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,21 +2834,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,13 +2858,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479770</v>
+        <v>479815</v>
       </c>
       <c r="R21" t="n">
-        <v>6953643</v>
+        <v>6953640</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2888,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,22 +2918,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117937373</v>
+        <v>117943674</v>
       </c>
       <c r="B22" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,34 +2946,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Slåttloken (Slåttloken), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479671</v>
+        <v>479569</v>
       </c>
       <c r="R22" t="n">
-        <v>6953727</v>
+        <v>6953686</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3000,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3015,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I hänsynskrävande surdråg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,7 +3047,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117942713</v>
+        <v>117939984</v>
       </c>
       <c r="B23" t="n">
         <v>78217</v>
@@ -3077,10 +3087,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479700</v>
+        <v>479815</v>
       </c>
       <c r="R23" t="n">
-        <v>6953611</v>
+        <v>6953640</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3112,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117941367</v>
+        <v>117942861</v>
       </c>
       <c r="B24" t="n">
-        <v>79069</v>
+        <v>78217</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,21 +3175,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479807</v>
+        <v>479638</v>
       </c>
       <c r="R24" t="n">
-        <v>6953285</v>
+        <v>6953606</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3261,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117938509</v>
+        <v>117941367</v>
       </c>
       <c r="B25" t="n">
-        <v>78216</v>
+        <v>79069</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,34 +3287,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479758</v>
+        <v>479807</v>
       </c>
       <c r="R25" t="n">
-        <v>6953656</v>
+        <v>6953285</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3373,7 +3383,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117936521</v>
+        <v>117941496</v>
       </c>
       <c r="B26" t="n">
         <v>78217</v>
@@ -3409,17 +3419,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479658</v>
+        <v>479807</v>
       </c>
       <c r="R26" t="n">
-        <v>6953757</v>
+        <v>6953276</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3448,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,22 +3483,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117941282</v>
+        <v>117938894</v>
       </c>
       <c r="B27" t="n">
-        <v>79561</v>
+        <v>78217</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,37 +3511,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479820</v>
+        <v>479776</v>
       </c>
       <c r="R27" t="n">
-        <v>6953242</v>
+        <v>6953614</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3560,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3580,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3585,22 +3595,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117941709</v>
+        <v>117938509</v>
       </c>
       <c r="B28" t="n">
-        <v>56499</v>
+        <v>78216</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,43 +3619,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479783</v>
+        <v>479758</v>
       </c>
       <c r="R28" t="n">
-        <v>6953379</v>
+        <v>6953656</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3714,7 +3719,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117937581</v>
+        <v>117938475</v>
       </c>
       <c r="B29" t="n">
         <v>78217</v>
@@ -3754,13 +3759,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479671</v>
+        <v>479758</v>
       </c>
       <c r="R29" t="n">
-        <v>6953726</v>
+        <v>6953656</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3789,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,22 +3819,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117941496</v>
+        <v>117942314</v>
       </c>
       <c r="B30" t="n">
-        <v>78217</v>
+        <v>90517</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3842,21 +3847,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3866,13 +3871,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479807</v>
+        <v>479741</v>
       </c>
       <c r="R30" t="n">
-        <v>6953276</v>
+        <v>6953389</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3901,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3926,22 +3931,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117940586</v>
+        <v>117941008</v>
       </c>
       <c r="B31" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3954,21 +3959,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3978,13 +3983,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479857</v>
+        <v>479958</v>
       </c>
       <c r="R31" t="n">
-        <v>6953493</v>
+        <v>6953321</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4013,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4038,22 +4043,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117941402</v>
+        <v>117938127</v>
       </c>
       <c r="B32" t="n">
-        <v>78217</v>
+        <v>56499</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4062,41 +4067,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479824</v>
+        <v>479712</v>
       </c>
       <c r="R32" t="n">
-        <v>6953250</v>
+        <v>6953704</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4125,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4135,7 +4145,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,19 +4160,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117938475</v>
+        <v>117941137</v>
       </c>
       <c r="B33" t="n">
         <v>78217</v>
@@ -4198,17 +4208,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479758</v>
+        <v>479903</v>
       </c>
       <c r="R33" t="n">
-        <v>6953656</v>
+        <v>6953255</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4237,7 +4247,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4247,7 +4257,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4262,22 +4272,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117942861</v>
+        <v>117940275</v>
       </c>
       <c r="B34" t="n">
-        <v>78217</v>
+        <v>79069</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4290,34 +4300,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479638</v>
+        <v>479803</v>
       </c>
       <c r="R34" t="n">
-        <v>6953606</v>
+        <v>6953633</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4386,10 +4396,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117943674</v>
+        <v>117940785</v>
       </c>
       <c r="B35" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4402,37 +4412,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Slåttloken (Slåttloken), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479569</v>
+        <v>479909</v>
       </c>
       <c r="R35" t="n">
-        <v>6953686</v>
+        <v>6953394</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4461,7 +4476,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4471,12 +4486,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>I hänsynskrävande surdråg</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,22 +4501,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117936812</v>
+        <v>117938218</v>
       </c>
       <c r="B36" t="n">
-        <v>90648</v>
+        <v>78217</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4515,25 +4525,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4543,13 +4553,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479671</v>
+        <v>479757</v>
       </c>
       <c r="R36" t="n">
-        <v>6953744</v>
+        <v>6953691</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4578,7 +4588,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4588,7 +4598,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4603,22 +4613,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117941840</v>
+        <v>117941402</v>
       </c>
       <c r="B37" t="n">
-        <v>5480</v>
+        <v>78217</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4631,21 +4641,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4655,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479804</v>
+        <v>479824</v>
       </c>
       <c r="R37" t="n">
-        <v>6953380</v>
+        <v>6953250</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4727,10 +4737,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117937050</v>
+        <v>117937373</v>
       </c>
       <c r="B38" t="n">
-        <v>56499</v>
+        <v>79098</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4739,43 +4749,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479672</v>
+        <v>479671</v>
       </c>
       <c r="R38" t="n">
-        <v>6953743</v>
+        <v>6953727</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4807,7 +4812,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4817,7 +4822,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4844,10 +4849,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117939942</v>
+        <v>117941282</v>
       </c>
       <c r="B39" t="n">
-        <v>79069</v>
+        <v>79561</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4860,34 +4865,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479815</v>
+        <v>479820</v>
       </c>
       <c r="R39" t="n">
-        <v>6953640</v>
+        <v>6953242</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4919,7 +4924,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4929,7 +4934,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4956,10 +4961,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117938127</v>
+        <v>117941078</v>
       </c>
       <c r="B40" t="n">
-        <v>56499</v>
+        <v>78480</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4968,43 +4973,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479712</v>
+        <v>479904</v>
       </c>
       <c r="R40" t="n">
-        <v>6953704</v>
+        <v>6953265</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117936812</v>
+        <v>117937050</v>
       </c>
       <c r="B2" t="n">
-        <v>90648</v>
+        <v>56500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479671</v>
+        <v>479672</v>
       </c>
       <c r="R2" t="n">
-        <v>6953744</v>
+        <v>6953743</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117942713</v>
+        <v>117937581</v>
       </c>
       <c r="B3" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479700</v>
+        <v>479671</v>
       </c>
       <c r="R3" t="n">
-        <v>6953611</v>
+        <v>6953726</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117938179</v>
+        <v>117939942</v>
       </c>
       <c r="B4" t="n">
-        <v>78125</v>
+        <v>79071</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479749</v>
+        <v>479815</v>
       </c>
       <c r="R4" t="n">
-        <v>6953702</v>
+        <v>6953640</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117938085</v>
+        <v>117939984</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>78219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479712</v>
+        <v>479815</v>
       </c>
       <c r="R5" t="n">
-        <v>6953704</v>
+        <v>6953640</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117942064</v>
+        <v>117937924</v>
       </c>
       <c r="B6" t="n">
-        <v>97857</v>
+        <v>96793</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479735</v>
+        <v>479739</v>
       </c>
       <c r="R6" t="n">
-        <v>6953521</v>
+        <v>6953704</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117937581</v>
+        <v>117943232</v>
       </c>
       <c r="B7" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,37 +1256,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479671</v>
+        <v>479604</v>
       </c>
       <c r="R7" t="n">
-        <v>6953726</v>
+        <v>6953667</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117941433</v>
+        <v>117942062</v>
       </c>
       <c r="B8" t="n">
-        <v>79589</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479796</v>
+        <v>479773</v>
       </c>
       <c r="R8" t="n">
-        <v>6953252</v>
+        <v>6953376</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1452,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117936521</v>
+        <v>117941709</v>
       </c>
       <c r="B9" t="n">
-        <v>78217</v>
+        <v>56500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,41 +1476,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479658</v>
+        <v>479783</v>
       </c>
       <c r="R9" t="n">
-        <v>6953757</v>
+        <v>6953379</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117941709</v>
+        <v>117938218</v>
       </c>
       <c r="B10" t="n">
-        <v>56499</v>
+        <v>78219</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,43 +1593,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479783</v>
+        <v>479757</v>
       </c>
       <c r="R10" t="n">
-        <v>6953379</v>
+        <v>6953691</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1688,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117937050</v>
+        <v>117941402</v>
       </c>
       <c r="B11" t="n">
-        <v>56499</v>
+        <v>78219</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,46 +1705,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479672</v>
+        <v>479824</v>
       </c>
       <c r="R11" t="n">
-        <v>6953743</v>
+        <v>6953250</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,22 +1793,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117941840</v>
+        <v>117938245</v>
       </c>
       <c r="B12" t="n">
-        <v>5480</v>
+        <v>78218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,34 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479804</v>
+        <v>479770</v>
       </c>
       <c r="R12" t="n">
-        <v>6953380</v>
+        <v>6953643</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117937924</v>
+        <v>117941282</v>
       </c>
       <c r="B13" t="n">
-        <v>96791</v>
+        <v>79563</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,41 +1929,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479739</v>
+        <v>479820</v>
       </c>
       <c r="R13" t="n">
-        <v>6953704</v>
+        <v>6953242</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,12 +2017,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2032,7 +2032,7 @@
         <v>117942027</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117940586</v>
+        <v>117936521</v>
       </c>
       <c r="B15" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479857</v>
+        <v>479658</v>
       </c>
       <c r="R15" t="n">
-        <v>6953493</v>
+        <v>6953757</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117938245</v>
+        <v>117941941</v>
       </c>
       <c r="B16" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,34 +2274,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479770</v>
+        <v>479761</v>
       </c>
       <c r="R16" t="n">
-        <v>6953643</v>
+        <v>6953483</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117942960</v>
+        <v>117940785</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,34 +2386,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479556</v>
+        <v>479909</v>
       </c>
       <c r="R17" t="n">
-        <v>6953566</v>
+        <v>6953394</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2482,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117942062</v>
+        <v>117943674</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,14 +2523,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Slåttloken (Slåttloken), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479773</v>
+        <v>479569</v>
       </c>
       <c r="R18" t="n">
-        <v>6953376</v>
+        <v>6953686</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2557,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2572,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I hänsynskrävande surdråg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117941941</v>
+        <v>117940586</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,37 +2620,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479761</v>
+        <v>479857</v>
       </c>
       <c r="R19" t="n">
-        <v>6953483</v>
+        <v>6953493</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2669,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,22 +2704,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117943232</v>
+        <v>117938179</v>
       </c>
       <c r="B20" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,34 +2732,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479604</v>
+        <v>479749</v>
       </c>
       <c r="R20" t="n">
-        <v>6953667</v>
+        <v>6953702</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2818,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117939942</v>
+        <v>117942064</v>
       </c>
       <c r="B21" t="n">
-        <v>79069</v>
+        <v>97859</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2830,41 +2840,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479815</v>
+        <v>479735</v>
       </c>
       <c r="R21" t="n">
-        <v>6953640</v>
+        <v>6953521</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2893,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,22 +2928,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117943674</v>
+        <v>117938509</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,37 +2956,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttloken (Slåttloken), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479569</v>
+        <v>479758</v>
       </c>
       <c r="R22" t="n">
-        <v>6953686</v>
+        <v>6953656</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3005,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,12 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I hänsynskrävande surdråg</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,22 +3040,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117939984</v>
+        <v>117938085</v>
       </c>
       <c r="B23" t="n">
-        <v>78217</v>
+        <v>79563</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,21 +3068,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3087,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479815</v>
+        <v>479712</v>
       </c>
       <c r="R23" t="n">
-        <v>6953640</v>
+        <v>6953704</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117942861</v>
+        <v>117938127</v>
       </c>
       <c r="B24" t="n">
-        <v>78217</v>
+        <v>56500</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3171,41 +3176,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479638</v>
+        <v>479712</v>
       </c>
       <c r="R24" t="n">
-        <v>6953606</v>
+        <v>6953704</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3234,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,22 +3269,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117941367</v>
+        <v>117941496</v>
       </c>
       <c r="B25" t="n">
-        <v>79069</v>
+        <v>78219</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,21 +3297,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3314,7 +3324,7 @@
         <v>479807</v>
       </c>
       <c r="R25" t="n">
-        <v>6953285</v>
+        <v>6953276</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3383,10 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117941496</v>
+        <v>117941433</v>
       </c>
       <c r="B26" t="n">
-        <v>78217</v>
+        <v>79591</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3395,25 +3405,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3423,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479807</v>
+        <v>479796</v>
       </c>
       <c r="R26" t="n">
-        <v>6953276</v>
+        <v>6953252</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3495,10 +3505,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117938894</v>
+        <v>117941367</v>
       </c>
       <c r="B27" t="n">
-        <v>78217</v>
+        <v>79071</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3511,34 +3521,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479776</v>
+        <v>479807</v>
       </c>
       <c r="R27" t="n">
-        <v>6953614</v>
+        <v>6953285</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3607,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117938509</v>
+        <v>117941137</v>
       </c>
       <c r="B28" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3623,37 +3633,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479758</v>
+        <v>479903</v>
       </c>
       <c r="R28" t="n">
-        <v>6953656</v>
+        <v>6953255</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3682,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,22 +3717,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117938475</v>
+        <v>117938894</v>
       </c>
       <c r="B29" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3759,10 +3769,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479758</v>
+        <v>479776</v>
       </c>
       <c r="R29" t="n">
-        <v>6953656</v>
+        <v>6953614</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3831,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117942314</v>
+        <v>117941840</v>
       </c>
       <c r="B30" t="n">
-        <v>90517</v>
+        <v>5480</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3847,21 +3857,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>101410</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3871,13 +3881,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479741</v>
+        <v>479804</v>
       </c>
       <c r="R30" t="n">
-        <v>6953389</v>
+        <v>6953380</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3906,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3931,22 +3941,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117941008</v>
+        <v>117940275</v>
       </c>
       <c r="B31" t="n">
-        <v>78480</v>
+        <v>79071</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,21 +3969,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3983,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479958</v>
+        <v>479803</v>
       </c>
       <c r="R31" t="n">
-        <v>6953321</v>
+        <v>6953633</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4055,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117938127</v>
+        <v>117938475</v>
       </c>
       <c r="B32" t="n">
-        <v>56499</v>
+        <v>78219</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4067,46 +4077,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479712</v>
+        <v>479758</v>
       </c>
       <c r="R32" t="n">
-        <v>6953704</v>
+        <v>6953656</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4135,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,22 +4165,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117941137</v>
+        <v>117942713</v>
       </c>
       <c r="B33" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4208,14 +4213,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479903</v>
+        <v>479700</v>
       </c>
       <c r="R33" t="n">
-        <v>6953255</v>
+        <v>6953611</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4247,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117940275</v>
+        <v>117942960</v>
       </c>
       <c r="B34" t="n">
-        <v>79069</v>
+        <v>79563</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4300,34 +4305,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479803</v>
+        <v>479556</v>
       </c>
       <c r="R34" t="n">
-        <v>6953633</v>
+        <v>6953566</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4396,10 +4401,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117940785</v>
+        <v>117936812</v>
       </c>
       <c r="B35" t="n">
-        <v>57287</v>
+        <v>90650</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4408,46 +4413,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479909</v>
+        <v>479671</v>
       </c>
       <c r="R35" t="n">
-        <v>6953394</v>
+        <v>6953744</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4501,22 +4501,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117938218</v>
+        <v>117942314</v>
       </c>
       <c r="B36" t="n">
-        <v>78217</v>
+        <v>90519</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4529,37 +4529,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479757</v>
+        <v>479741</v>
       </c>
       <c r="R36" t="n">
-        <v>6953691</v>
+        <v>6953389</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,22 +4613,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117941402</v>
+        <v>117942861</v>
       </c>
       <c r="B37" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479824</v>
+        <v>479638</v>
       </c>
       <c r="R37" t="n">
-        <v>6953250</v>
+        <v>6953606</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4737,10 +4737,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117937373</v>
+        <v>117941078</v>
       </c>
       <c r="B38" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4753,34 +4753,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479671</v>
+        <v>479904</v>
       </c>
       <c r="R38" t="n">
-        <v>6953727</v>
+        <v>6953265</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4849,10 +4849,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117941282</v>
+        <v>117941008</v>
       </c>
       <c r="B39" t="n">
-        <v>79561</v>
+        <v>78482</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4865,37 +4865,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479820</v>
+        <v>479958</v>
       </c>
       <c r="R39" t="n">
-        <v>6953242</v>
+        <v>6953321</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4949,22 +4949,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117941078</v>
+        <v>117937373</v>
       </c>
       <c r="B40" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4977,34 +4977,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479904</v>
+        <v>479671</v>
       </c>
       <c r="R40" t="n">
-        <v>6953265</v>
+        <v>6953727</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -3052,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117938085</v>
+        <v>117938127</v>
       </c>
       <c r="B23" t="n">
-        <v>79563</v>
+        <v>56500</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,28 +3064,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
@@ -3127,7 +3132,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3142,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3169,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117938127</v>
+        <v>117938085</v>
       </c>
       <c r="B24" t="n">
-        <v>56500</v>
+        <v>79563</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3176,33 +3181,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3617,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117941137</v>
+        <v>117941840</v>
       </c>
       <c r="B28" t="n">
-        <v>78219</v>
+        <v>5480</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3633,21 +3633,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3657,13 +3657,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479903</v>
+        <v>479804</v>
       </c>
       <c r="R28" t="n">
-        <v>6953255</v>
+        <v>6953380</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3717,19 +3717,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117938894</v>
+        <v>117941137</v>
       </c>
       <c r="B29" t="n">
         <v>78219</v>
@@ -3765,17 +3765,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479776</v>
+        <v>479903</v>
       </c>
       <c r="R29" t="n">
-        <v>6953614</v>
+        <v>6953255</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3829,22 +3829,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117941840</v>
+        <v>117938894</v>
       </c>
       <c r="B30" t="n">
-        <v>5480</v>
+        <v>78219</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,34 +3857,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479804</v>
+        <v>479776</v>
       </c>
       <c r="R30" t="n">
-        <v>6953380</v>
+        <v>6953614</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -4839,7 +4839,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117940785</v>
+        <v>117942027</v>
       </c>
       <c r="B39" t="n">
         <v>57290</v>
@@ -4880,14 +4880,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget (Björnberget), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479909</v>
+        <v>479728</v>
       </c>
       <c r="R39" t="n">
-        <v>6953394</v>
+        <v>6953486</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117942027</v>
+        <v>117940785</v>
       </c>
       <c r="B40" t="n">
         <v>57290</v>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479728</v>
+        <v>479909</v>
       </c>
       <c r="R40" t="n">
-        <v>6953486</v>
+        <v>6953394</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5175,10 +5175,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122185998</v>
+        <v>122186015</v>
       </c>
       <c r="B42" t="n">
-        <v>92067</v>
+        <v>78290</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5187,25 +5187,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479583</v>
+        <v>479648</v>
       </c>
       <c r="R42" t="n">
-        <v>6953383</v>
+        <v>6953743</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5245,12 +5245,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5277,10 +5277,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186016</v>
+        <v>122186011</v>
       </c>
       <c r="B43" t="n">
-        <v>5489</v>
+        <v>78029</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5293,21 +5293,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101410</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479650</v>
+        <v>479657</v>
       </c>
       <c r="R43" t="n">
-        <v>6953743</v>
+        <v>6953720</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122186015</v>
+        <v>122185999</v>
       </c>
       <c r="B45" t="n">
-        <v>78290</v>
+        <v>92055</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5493,25 +5493,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479648</v>
+        <v>479600</v>
       </c>
       <c r="R45" t="n">
-        <v>6953743</v>
+        <v>6953419</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5551,12 +5551,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5583,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122186018</v>
+        <v>122186002</v>
       </c>
       <c r="B46" t="n">
-        <v>78671</v>
+        <v>78381</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5595,25 +5595,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479659</v>
+        <v>479905</v>
       </c>
       <c r="R46" t="n">
-        <v>6953756</v>
+        <v>6953264</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5685,7 +5685,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186014</v>
+        <v>122186017</v>
       </c>
       <c r="B47" t="n">
         <v>78382</v>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479647</v>
+        <v>479660</v>
       </c>
       <c r="R47" t="n">
-        <v>6953742</v>
+        <v>6953756</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122186002</v>
+        <v>122186018</v>
       </c>
       <c r="B48" t="n">
-        <v>78381</v>
+        <v>78671</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5799,25 +5799,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479905</v>
+        <v>479659</v>
       </c>
       <c r="R48" t="n">
-        <v>6953264</v>
+        <v>6953756</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5889,7 +5889,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122186017</v>
+        <v>122186010</v>
       </c>
       <c r="B49" t="n">
         <v>78382</v>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479660</v>
+        <v>479657</v>
       </c>
       <c r="R49" t="n">
-        <v>6953756</v>
+        <v>6953719</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5991,7 +5991,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122186010</v>
+        <v>122186014</v>
       </c>
       <c r="B50" t="n">
         <v>78382</v>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479657</v>
+        <v>479647</v>
       </c>
       <c r="R50" t="n">
-        <v>6953719</v>
+        <v>6953742</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122185999</v>
+        <v>122186012</v>
       </c>
       <c r="B51" t="n">
-        <v>92055</v>
+        <v>78029</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6105,25 +6105,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479600</v>
+        <v>479642</v>
       </c>
       <c r="R51" t="n">
-        <v>6953419</v>
+        <v>6953724</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6163,12 +6163,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6195,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122186011</v>
+        <v>122186016</v>
       </c>
       <c r="B52" t="n">
-        <v>78029</v>
+        <v>5489</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6211,21 +6211,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>101410</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479657</v>
+        <v>479650</v>
       </c>
       <c r="R52" t="n">
-        <v>6953720</v>
+        <v>6953743</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6297,10 +6297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122186012</v>
+        <v>122185998</v>
       </c>
       <c r="B53" t="n">
-        <v>78029</v>
+        <v>92067</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6309,25 +6309,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479642</v>
+        <v>479583</v>
       </c>
       <c r="R53" t="n">
-        <v>6953724</v>
+        <v>6953383</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5991,10 +5991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122186014</v>
+        <v>122186016</v>
       </c>
       <c r="B50" t="n">
-        <v>78382</v>
+        <v>5489</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479647</v>
+        <v>479650</v>
       </c>
       <c r="R50" t="n">
-        <v>6953742</v>
+        <v>6953743</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122186016</v>
+        <v>122186014</v>
       </c>
       <c r="B52" t="n">
-        <v>5489</v>
+        <v>78382</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6211,21 +6211,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479650</v>
+        <v>479647</v>
       </c>
       <c r="R52" t="n">
-        <v>6953743</v>
+        <v>6953742</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122186000</v>
+        <v>122186014</v>
       </c>
       <c r="B41" t="n">
-        <v>79754</v>
+        <v>78383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,25 +5085,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479720</v>
+        <v>479647</v>
       </c>
       <c r="R41" t="n">
-        <v>6953578</v>
+        <v>6953742</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,10 +5175,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122186015</v>
+        <v>122186018</v>
       </c>
       <c r="B42" t="n">
-        <v>78290</v>
+        <v>78672</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5187,25 +5187,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479648</v>
+        <v>479659</v>
       </c>
       <c r="R42" t="n">
-        <v>6953743</v>
+        <v>6953756</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186011</v>
+        <v>122186012</v>
       </c>
       <c r="B43" t="n">
-        <v>78029</v>
+        <v>78030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479657</v>
+        <v>479642</v>
       </c>
       <c r="R43" t="n">
-        <v>6953720</v>
+        <v>6953724</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122186004</v>
+        <v>122186016</v>
       </c>
       <c r="B44" t="n">
-        <v>78382</v>
+        <v>5489</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479742</v>
+        <v>479650</v>
       </c>
       <c r="R44" t="n">
-        <v>6953544</v>
+        <v>6953743</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5449,12 +5449,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5481,10 +5481,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122185999</v>
+        <v>122186004</v>
       </c>
       <c r="B45" t="n">
-        <v>92055</v>
+        <v>78383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5493,25 +5493,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479600</v>
+        <v>479742</v>
       </c>
       <c r="R45" t="n">
-        <v>6953419</v>
+        <v>6953544</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122186002</v>
+        <v>122186010</v>
       </c>
       <c r="B46" t="n">
-        <v>78381</v>
+        <v>78383</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479905</v>
+        <v>479657</v>
       </c>
       <c r="R46" t="n">
-        <v>6953264</v>
+        <v>6953719</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5685,10 +5685,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186017</v>
+        <v>122186000</v>
       </c>
       <c r="B47" t="n">
-        <v>78382</v>
+        <v>79755</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5697,25 +5697,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479660</v>
+        <v>479720</v>
       </c>
       <c r="R47" t="n">
-        <v>6953756</v>
+        <v>6953578</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5787,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122186018</v>
+        <v>122186002</v>
       </c>
       <c r="B48" t="n">
-        <v>78671</v>
+        <v>78382</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5799,25 +5799,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479659</v>
+        <v>479905</v>
       </c>
       <c r="R48" t="n">
-        <v>6953756</v>
+        <v>6953264</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5889,10 +5889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122186010</v>
+        <v>122185999</v>
       </c>
       <c r="B49" t="n">
-        <v>78382</v>
+        <v>92065</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5901,25 +5901,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479657</v>
+        <v>479600</v>
       </c>
       <c r="R49" t="n">
-        <v>6953719</v>
+        <v>6953419</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5991,10 +5991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122186016</v>
+        <v>122186017</v>
       </c>
       <c r="B50" t="n">
-        <v>5489</v>
+        <v>78383</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479650</v>
+        <v>479660</v>
       </c>
       <c r="R50" t="n">
-        <v>6953743</v>
+        <v>6953756</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122186012</v>
+        <v>122186011</v>
       </c>
       <c r="B51" t="n">
-        <v>78029</v>
+        <v>78030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479642</v>
+        <v>479657</v>
       </c>
       <c r="R51" t="n">
-        <v>6953724</v>
+        <v>6953720</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122186014</v>
+        <v>122185998</v>
       </c>
       <c r="B52" t="n">
-        <v>78382</v>
+        <v>92077</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6207,25 +6207,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479647</v>
+        <v>479583</v>
       </c>
       <c r="R52" t="n">
-        <v>6953742</v>
+        <v>6953383</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6265,12 +6265,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6297,10 +6297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122185998</v>
+        <v>122186015</v>
       </c>
       <c r="B53" t="n">
-        <v>92067</v>
+        <v>78291</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6309,25 +6309,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479583</v>
+        <v>479648</v>
       </c>
       <c r="R53" t="n">
-        <v>6953383</v>
+        <v>6953743</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122186014</v>
+        <v>122186018</v>
       </c>
       <c r="B41" t="n">
-        <v>78383</v>
+        <v>78672</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,25 +5085,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479647</v>
+        <v>479659</v>
       </c>
       <c r="R41" t="n">
-        <v>6953742</v>
+        <v>6953756</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5175,10 +5175,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122186018</v>
+        <v>122186017</v>
       </c>
       <c r="B42" t="n">
-        <v>78672</v>
+        <v>78383</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5187,25 +5187,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479659</v>
+        <v>479660</v>
       </c>
       <c r="R42" t="n">
         <v>6953756</v>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186012</v>
+        <v>122186016</v>
       </c>
       <c r="B43" t="n">
-        <v>78030</v>
+        <v>5489</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5293,21 +5293,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>101410</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479642</v>
+        <v>479650</v>
       </c>
       <c r="R43" t="n">
-        <v>6953724</v>
+        <v>6953743</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122186016</v>
+        <v>122186002</v>
       </c>
       <c r="B44" t="n">
-        <v>5489</v>
+        <v>78382</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>101410</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479650</v>
+        <v>479905</v>
       </c>
       <c r="R44" t="n">
-        <v>6953743</v>
+        <v>6953264</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5449,12 +5449,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5481,10 +5481,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122186004</v>
+        <v>122186015</v>
       </c>
       <c r="B45" t="n">
-        <v>78383</v>
+        <v>78291</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5497,21 +5497,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479742</v>
+        <v>479648</v>
       </c>
       <c r="R45" t="n">
-        <v>6953544</v>
+        <v>6953743</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5551,12 +5551,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5583,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122186010</v>
+        <v>122186011</v>
       </c>
       <c r="B46" t="n">
-        <v>78383</v>
+        <v>78030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5626,7 +5626,7 @@
         <v>479657</v>
       </c>
       <c r="R46" t="n">
-        <v>6953719</v>
+        <v>6953720</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186000</v>
+        <v>122186010</v>
       </c>
       <c r="B47" t="n">
-        <v>79755</v>
+        <v>78383</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5697,25 +5697,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479720</v>
+        <v>479657</v>
       </c>
       <c r="R47" t="n">
-        <v>6953578</v>
+        <v>6953719</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5787,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122186002</v>
+        <v>122186004</v>
       </c>
       <c r="B48" t="n">
-        <v>78382</v>
+        <v>78383</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5803,21 +5803,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479905</v>
+        <v>479742</v>
       </c>
       <c r="R48" t="n">
-        <v>6953264</v>
+        <v>6953544</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5889,10 +5889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122185999</v>
+        <v>122185998</v>
       </c>
       <c r="B49" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5905,21 +5905,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479600</v>
+        <v>479583</v>
       </c>
       <c r="R49" t="n">
-        <v>6953419</v>
+        <v>6953383</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5991,10 +5991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122186017</v>
+        <v>122186000</v>
       </c>
       <c r="B50" t="n">
-        <v>78383</v>
+        <v>79755</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6003,25 +6003,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479660</v>
+        <v>479720</v>
       </c>
       <c r="R50" t="n">
-        <v>6953756</v>
+        <v>6953578</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6093,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122186011</v>
+        <v>122186014</v>
       </c>
       <c r="B51" t="n">
-        <v>78030</v>
+        <v>78383</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6109,21 +6109,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479657</v>
+        <v>479647</v>
       </c>
       <c r="R51" t="n">
-        <v>6953720</v>
+        <v>6953742</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122185998</v>
+        <v>122186012</v>
       </c>
       <c r="B52" t="n">
-        <v>92077</v>
+        <v>78030</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6207,25 +6207,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4366</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479583</v>
+        <v>479642</v>
       </c>
       <c r="R52" t="n">
-        <v>6953383</v>
+        <v>6953724</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6265,12 +6265,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6297,10 +6297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122186015</v>
+        <v>122185999</v>
       </c>
       <c r="B53" t="n">
-        <v>78291</v>
+        <v>92065</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6309,25 +6309,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479648</v>
+        <v>479600</v>
       </c>
       <c r="R53" t="n">
-        <v>6953743</v>
+        <v>6953419</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122186018</v>
+        <v>122186002</v>
       </c>
       <c r="B41" t="n">
-        <v>78672</v>
+        <v>78387</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,25 +5085,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479659</v>
+        <v>479905</v>
       </c>
       <c r="R41" t="n">
-        <v>6953756</v>
+        <v>6953264</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,10 +5175,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122186017</v>
+        <v>122186015</v>
       </c>
       <c r="B42" t="n">
-        <v>78383</v>
+        <v>78296</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479660</v>
+        <v>479648</v>
       </c>
       <c r="R42" t="n">
-        <v>6953756</v>
+        <v>6953743</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122186002</v>
+        <v>122186004</v>
       </c>
       <c r="B44" t="n">
-        <v>78382</v>
+        <v>78388</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479905</v>
+        <v>479742</v>
       </c>
       <c r="R44" t="n">
-        <v>6953264</v>
+        <v>6953544</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122186015</v>
+        <v>122185998</v>
       </c>
       <c r="B45" t="n">
-        <v>78291</v>
+        <v>92089</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5493,25 +5493,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479648</v>
+        <v>479583</v>
       </c>
       <c r="R45" t="n">
-        <v>6953743</v>
+        <v>6953383</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5551,12 +5551,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5586,7 +5586,7 @@
         <v>122186011</v>
       </c>
       <c r="B46" t="n">
-        <v>78030</v>
+        <v>78035</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186010</v>
+        <v>122186014</v>
       </c>
       <c r="B47" t="n">
-        <v>78383</v>
+        <v>78388</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479657</v>
+        <v>479647</v>
       </c>
       <c r="R47" t="n">
-        <v>6953719</v>
+        <v>6953742</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122186004</v>
+        <v>122185999</v>
       </c>
       <c r="B48" t="n">
-        <v>78383</v>
+        <v>92077</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5799,25 +5799,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479742</v>
+        <v>479600</v>
       </c>
       <c r="R48" t="n">
-        <v>6953544</v>
+        <v>6953419</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5889,10 +5889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122185998</v>
+        <v>122186000</v>
       </c>
       <c r="B49" t="n">
-        <v>92077</v>
+        <v>79760</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5905,21 +5905,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4366</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479583</v>
+        <v>479720</v>
       </c>
       <c r="R49" t="n">
-        <v>6953383</v>
+        <v>6953578</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5991,10 +5991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122186000</v>
+        <v>122186018</v>
       </c>
       <c r="B50" t="n">
-        <v>79755</v>
+        <v>78677</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479720</v>
+        <v>479659</v>
       </c>
       <c r="R50" t="n">
-        <v>6953578</v>
+        <v>6953756</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6093,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122186014</v>
+        <v>122186012</v>
       </c>
       <c r="B51" t="n">
-        <v>78383</v>
+        <v>78035</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6109,21 +6109,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479647</v>
+        <v>479642</v>
       </c>
       <c r="R51" t="n">
-        <v>6953742</v>
+        <v>6953724</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122186012</v>
+        <v>122186017</v>
       </c>
       <c r="B52" t="n">
-        <v>78030</v>
+        <v>78388</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6211,21 +6211,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479642</v>
+        <v>479660</v>
       </c>
       <c r="R52" t="n">
-        <v>6953724</v>
+        <v>6953756</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6297,10 +6297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122185999</v>
+        <v>122186010</v>
       </c>
       <c r="B53" t="n">
-        <v>92065</v>
+        <v>78388</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6309,25 +6309,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479600</v>
+        <v>479657</v>
       </c>
       <c r="R53" t="n">
-        <v>6953419</v>
+        <v>6953719</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122186002</v>
+        <v>122186010</v>
       </c>
       <c r="B41" t="n">
-        <v>78387</v>
+        <v>78388</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479905</v>
+        <v>479657</v>
       </c>
       <c r="R41" t="n">
-        <v>6953264</v>
+        <v>6953719</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,10 +5175,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122186015</v>
+        <v>122186016</v>
       </c>
       <c r="B42" t="n">
-        <v>78296</v>
+        <v>5489</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479648</v>
+        <v>479650</v>
       </c>
       <c r="R42" t="n">
         <v>6953743</v>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186016</v>
+        <v>122186011</v>
       </c>
       <c r="B43" t="n">
-        <v>5489</v>
+        <v>78035</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5293,21 +5293,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101410</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479650</v>
+        <v>479657</v>
       </c>
       <c r="R43" t="n">
-        <v>6953743</v>
+        <v>6953720</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122186004</v>
+        <v>122185999</v>
       </c>
       <c r="B44" t="n">
-        <v>78388</v>
+        <v>92082</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5391,25 +5391,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479742</v>
+        <v>479600</v>
       </c>
       <c r="R44" t="n">
-        <v>6953544</v>
+        <v>6953419</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122185998</v>
+        <v>122186014</v>
       </c>
       <c r="B45" t="n">
-        <v>92089</v>
+        <v>78388</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5493,25 +5493,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479583</v>
+        <v>479647</v>
       </c>
       <c r="R45" t="n">
-        <v>6953383</v>
+        <v>6953742</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5551,12 +5551,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5583,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122186011</v>
+        <v>122186015</v>
       </c>
       <c r="B46" t="n">
-        <v>78035</v>
+        <v>78296</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479657</v>
+        <v>479648</v>
       </c>
       <c r="R46" t="n">
-        <v>6953720</v>
+        <v>6953743</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5685,7 +5685,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186014</v>
+        <v>122186004</v>
       </c>
       <c r="B47" t="n">
         <v>78388</v>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479647</v>
+        <v>479742</v>
       </c>
       <c r="R47" t="n">
-        <v>6953742</v>
+        <v>6953544</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5787,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122185999</v>
+        <v>122186002</v>
       </c>
       <c r="B48" t="n">
-        <v>92077</v>
+        <v>78387</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5799,25 +5799,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479600</v>
+        <v>479905</v>
       </c>
       <c r="R48" t="n">
-        <v>6953419</v>
+        <v>6953264</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5889,10 +5889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122186000</v>
+        <v>122186017</v>
       </c>
       <c r="B49" t="n">
-        <v>79760</v>
+        <v>78388</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5901,25 +5901,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479720</v>
+        <v>479660</v>
       </c>
       <c r="R49" t="n">
-        <v>6953578</v>
+        <v>6953756</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5991,10 +5991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122186018</v>
+        <v>122185998</v>
       </c>
       <c r="B50" t="n">
-        <v>78677</v>
+        <v>92094</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479659</v>
+        <v>479583</v>
       </c>
       <c r="R50" t="n">
-        <v>6953756</v>
+        <v>6953383</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6093,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122186012</v>
+        <v>122186000</v>
       </c>
       <c r="B51" t="n">
-        <v>78035</v>
+        <v>79760</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6105,25 +6105,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6437</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479642</v>
+        <v>479720</v>
       </c>
       <c r="R51" t="n">
-        <v>6953724</v>
+        <v>6953578</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6163,12 +6163,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6195,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122186017</v>
+        <v>122186018</v>
       </c>
       <c r="B52" t="n">
-        <v>78388</v>
+        <v>78677</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6207,25 +6207,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479660</v>
+        <v>479659</v>
       </c>
       <c r="R52" t="n">
         <v>6953756</v>
@@ -6297,10 +6297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122186010</v>
+        <v>122186012</v>
       </c>
       <c r="B53" t="n">
-        <v>78388</v>
+        <v>78035</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6313,21 +6313,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479657</v>
+        <v>479642</v>
       </c>
       <c r="R53" t="n">
-        <v>6953719</v>
+        <v>6953724</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122186010</v>
+        <v>122185998</v>
       </c>
       <c r="B41" t="n">
-        <v>78388</v>
+        <v>92099</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,25 +5085,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>4366</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5113,10 +5108,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479657</v>
+        <v>479583</v>
       </c>
       <c r="R41" t="n">
-        <v>6953719</v>
+        <v>6953383</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5143,12 +5138,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,10 +5170,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122186016</v>
+        <v>122186011</v>
       </c>
       <c r="B42" t="n">
-        <v>5489</v>
+        <v>78036</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5191,21 +5186,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101410</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Reliktbock</t>
-        </is>
+        <v>6437</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,10 +5205,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479650</v>
+        <v>479657</v>
       </c>
       <c r="R42" t="n">
-        <v>6953743</v>
+        <v>6953720</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5277,10 +5267,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186011</v>
+        <v>122186012</v>
       </c>
       <c r="B43" t="n">
-        <v>78035</v>
+        <v>78036</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5295,11 +5285,6 @@
       <c r="E43" t="n">
         <v>6437</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Calicium denigratum</t>
@@ -5317,10 +5302,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479657</v>
+        <v>479642</v>
       </c>
       <c r="R43" t="n">
-        <v>6953720</v>
+        <v>6953724</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5379,10 +5364,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122185999</v>
+        <v>122186017</v>
       </c>
       <c r="B44" t="n">
-        <v>92082</v>
+        <v>78389</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5391,25 +5376,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5419,10 +5399,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479600</v>
+        <v>479660</v>
       </c>
       <c r="R44" t="n">
-        <v>6953419</v>
+        <v>6953756</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5449,12 +5429,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5481,10 +5461,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122186014</v>
+        <v>122186000</v>
       </c>
       <c r="B45" t="n">
-        <v>78388</v>
+        <v>79761</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5493,25 +5473,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6461</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5521,10 +5496,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479647</v>
+        <v>479720</v>
       </c>
       <c r="R45" t="n">
-        <v>6953742</v>
+        <v>6953578</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5551,12 +5526,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5583,10 +5558,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122186015</v>
+        <v>122186004</v>
       </c>
       <c r="B46" t="n">
-        <v>78296</v>
+        <v>78389</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5599,21 +5574,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5623,10 +5593,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479648</v>
+        <v>479742</v>
       </c>
       <c r="R46" t="n">
-        <v>6953743</v>
+        <v>6953544</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5653,12 +5623,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5685,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186004</v>
+        <v>122186015</v>
       </c>
       <c r="B47" t="n">
-        <v>78388</v>
+        <v>78297</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5701,21 +5671,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>353</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5725,10 +5690,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479742</v>
+        <v>479648</v>
       </c>
       <c r="R47" t="n">
-        <v>6953544</v>
+        <v>6953743</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5755,12 +5720,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5787,10 +5752,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122186002</v>
+        <v>122185999</v>
       </c>
       <c r="B48" t="n">
-        <v>78387</v>
+        <v>92087</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5799,25 +5764,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5827,10 +5787,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479905</v>
+        <v>479600</v>
       </c>
       <c r="R48" t="n">
-        <v>6953264</v>
+        <v>6953419</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5889,7 +5849,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122186017</v>
+        <v>122186002</v>
       </c>
       <c r="B49" t="n">
         <v>78388</v>
@@ -5905,21 +5865,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6446</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5929,10 +5884,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479660</v>
+        <v>479905</v>
       </c>
       <c r="R49" t="n">
-        <v>6953756</v>
+        <v>6953264</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5959,12 +5914,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5991,10 +5946,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122185998</v>
+        <v>122186016</v>
       </c>
       <c r="B50" t="n">
-        <v>92094</v>
+        <v>5489</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6003,25 +5958,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp</t>
-        </is>
+        <v>101410</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +5981,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479583</v>
+        <v>479650</v>
       </c>
       <c r="R50" t="n">
-        <v>6953383</v>
+        <v>6953743</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6061,12 +6011,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6093,10 +6043,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122186000</v>
+        <v>122186018</v>
       </c>
       <c r="B51" t="n">
-        <v>79760</v>
+        <v>78678</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6109,21 +6059,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
+        <v>6434</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6133,10 +6078,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479720</v>
+        <v>479659</v>
       </c>
       <c r="R51" t="n">
-        <v>6953578</v>
+        <v>6953756</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6163,12 +6108,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6195,10 +6140,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122186018</v>
+        <v>122186010</v>
       </c>
       <c r="B52" t="n">
-        <v>78677</v>
+        <v>78389</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6207,25 +6152,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6434</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Nästlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6235,10 +6175,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479659</v>
+        <v>479657</v>
       </c>
       <c r="R52" t="n">
-        <v>6953756</v>
+        <v>6953719</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6297,10 +6237,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122186012</v>
+        <v>122186014</v>
       </c>
       <c r="B53" t="n">
-        <v>78035</v>
+        <v>78389</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6313,21 +6253,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6337,10 +6272,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479642</v>
+        <v>479647</v>
       </c>
       <c r="R53" t="n">
-        <v>6953724</v>
+        <v>6953742</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5655,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186015</v>
+        <v>122185999</v>
       </c>
       <c r="B47" t="n">
-        <v>78297</v>
+        <v>92087</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5667,20 +5667,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479648</v>
+        <v>479600</v>
       </c>
       <c r="R47" t="n">
-        <v>6953743</v>
+        <v>6953419</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5720,12 +5720,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,10 +5752,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122185999</v>
+        <v>122186015</v>
       </c>
       <c r="B48" t="n">
-        <v>92087</v>
+        <v>78297</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5764,20 +5764,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479600</v>
+        <v>479648</v>
       </c>
       <c r="R48" t="n">
-        <v>6953419</v>
+        <v>6953743</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122185998</v>
+        <v>122186000</v>
       </c>
       <c r="B41" t="n">
-        <v>92099</v>
+        <v>79765</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5089,16 +5089,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>6461</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5108,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479583</v>
+        <v>479720</v>
       </c>
       <c r="R41" t="n">
-        <v>6953383</v>
+        <v>6953578</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5170,10 +5175,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122186011</v>
+        <v>122186004</v>
       </c>
       <c r="B42" t="n">
-        <v>78036</v>
+        <v>78393</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5186,16 +5191,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5205,10 +5215,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479657</v>
+        <v>479742</v>
       </c>
       <c r="R42" t="n">
-        <v>6953720</v>
+        <v>6953544</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5235,12 +5245,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,10 +5277,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186012</v>
+        <v>122186015</v>
       </c>
       <c r="B43" t="n">
-        <v>78036</v>
+        <v>78301</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5283,16 +5293,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>353</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5302,10 +5317,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479642</v>
+        <v>479648</v>
       </c>
       <c r="R43" t="n">
-        <v>6953724</v>
+        <v>6953743</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5364,10 +5379,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122186017</v>
+        <v>122186010</v>
       </c>
       <c r="B44" t="n">
-        <v>78389</v>
+        <v>78393</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5382,6 +5397,11 @@
       <c r="E44" t="n">
         <v>228912</v>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Carbonicola myrmecina</t>
@@ -5399,10 +5419,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479660</v>
+        <v>479657</v>
       </c>
       <c r="R44" t="n">
-        <v>6953756</v>
+        <v>6953719</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5461,10 +5481,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122186000</v>
+        <v>122185998</v>
       </c>
       <c r="B45" t="n">
-        <v>79761</v>
+        <v>92112</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5477,16 +5497,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>4366</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5496,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479720</v>
+        <v>479583</v>
       </c>
       <c r="R45" t="n">
-        <v>6953578</v>
+        <v>6953383</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5558,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122186004</v>
+        <v>122185999</v>
       </c>
       <c r="B46" t="n">
-        <v>78389</v>
+        <v>92100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5570,20 +5595,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>4364</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5593,10 +5623,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479742</v>
+        <v>479600</v>
       </c>
       <c r="R46" t="n">
-        <v>6953544</v>
+        <v>6953419</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5655,10 +5685,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122185999</v>
+        <v>122186017</v>
       </c>
       <c r="B47" t="n">
-        <v>92087</v>
+        <v>78393</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5667,20 +5697,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5690,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479600</v>
+        <v>479660</v>
       </c>
       <c r="R47" t="n">
-        <v>6953419</v>
+        <v>6953756</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5720,12 +5755,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5752,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122186015</v>
+        <v>122186002</v>
       </c>
       <c r="B48" t="n">
-        <v>78297</v>
+        <v>78392</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5768,16 +5803,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6446</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5787,10 +5827,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479648</v>
+        <v>479905</v>
       </c>
       <c r="R48" t="n">
-        <v>6953743</v>
+        <v>6953264</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5817,12 +5857,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5849,10 +5889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122186002</v>
+        <v>122186011</v>
       </c>
       <c r="B49" t="n">
-        <v>78388</v>
+        <v>78040</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5865,16 +5905,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6437</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5884,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479905</v>
+        <v>479657</v>
       </c>
       <c r="R49" t="n">
-        <v>6953264</v>
+        <v>6953720</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5914,12 +5959,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5946,10 +5991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122186016</v>
+        <v>122186012</v>
       </c>
       <c r="B50" t="n">
-        <v>5489</v>
+        <v>78040</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5962,16 +6007,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101410</v>
+        <v>6437</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5981,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479650</v>
+        <v>479642</v>
       </c>
       <c r="R50" t="n">
-        <v>6953743</v>
+        <v>6953724</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6043,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122186018</v>
+        <v>122186016</v>
       </c>
       <c r="B51" t="n">
-        <v>78678</v>
+        <v>5489</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6055,20 +6105,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>101410</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6078,10 +6133,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479659</v>
+        <v>479650</v>
       </c>
       <c r="R51" t="n">
-        <v>6953756</v>
+        <v>6953743</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6140,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122186010</v>
+        <v>122186014</v>
       </c>
       <c r="B52" t="n">
-        <v>78389</v>
+        <v>78393</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6158,6 +6213,11 @@
       <c r="E52" t="n">
         <v>228912</v>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>Carbonicola myrmecina</t>
@@ -6175,10 +6235,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479657</v>
+        <v>479647</v>
       </c>
       <c r="R52" t="n">
-        <v>6953719</v>
+        <v>6953742</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6237,10 +6297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122186014</v>
+        <v>122186018</v>
       </c>
       <c r="B53" t="n">
-        <v>78389</v>
+        <v>78682</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6249,20 +6309,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6434</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6272,10 +6337,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479647</v>
+        <v>479659</v>
       </c>
       <c r="R53" t="n">
-        <v>6953742</v>
+        <v>6953756</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122186000</v>
+        <v>122186017</v>
       </c>
       <c r="B41" t="n">
-        <v>79765</v>
+        <v>78393</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,25 +5085,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479720</v>
+        <v>479660</v>
       </c>
       <c r="R41" t="n">
-        <v>6953578</v>
+        <v>6953756</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5277,10 +5277,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186015</v>
+        <v>122186011</v>
       </c>
       <c r="B43" t="n">
-        <v>78301</v>
+        <v>78040</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5293,21 +5293,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479648</v>
+        <v>479657</v>
       </c>
       <c r="R43" t="n">
-        <v>6953743</v>
+        <v>6953720</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122186010</v>
+        <v>122186002</v>
       </c>
       <c r="B44" t="n">
-        <v>78393</v>
+        <v>78392</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479657</v>
+        <v>479905</v>
       </c>
       <c r="R44" t="n">
-        <v>6953719</v>
+        <v>6953264</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5449,12 +5449,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5481,10 +5481,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122185998</v>
+        <v>122186018</v>
       </c>
       <c r="B45" t="n">
-        <v>92112</v>
+        <v>78682</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5497,21 +5497,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479583</v>
+        <v>479659</v>
       </c>
       <c r="R45" t="n">
-        <v>6953383</v>
+        <v>6953756</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5551,12 +5551,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5583,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122185999</v>
+        <v>122186010</v>
       </c>
       <c r="B46" t="n">
-        <v>92100</v>
+        <v>78393</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5595,25 +5595,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479600</v>
+        <v>479657</v>
       </c>
       <c r="R46" t="n">
-        <v>6953419</v>
+        <v>6953719</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5685,10 +5685,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186017</v>
+        <v>122186016</v>
       </c>
       <c r="B47" t="n">
-        <v>78393</v>
+        <v>5489</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479660</v>
+        <v>479650</v>
       </c>
       <c r="R47" t="n">
-        <v>6953756</v>
+        <v>6953743</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122186002</v>
+        <v>122186012</v>
       </c>
       <c r="B48" t="n">
-        <v>78392</v>
+        <v>78040</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5803,21 +5803,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479905</v>
+        <v>479642</v>
       </c>
       <c r="R48" t="n">
-        <v>6953264</v>
+        <v>6953724</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5889,10 +5889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122186011</v>
+        <v>122186000</v>
       </c>
       <c r="B49" t="n">
-        <v>78040</v>
+        <v>79765</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5901,25 +5901,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479657</v>
+        <v>479720</v>
       </c>
       <c r="R49" t="n">
-        <v>6953720</v>
+        <v>6953578</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5991,10 +5991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122186012</v>
+        <v>122185998</v>
       </c>
       <c r="B50" t="n">
-        <v>78040</v>
+        <v>92125</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6003,25 +6003,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479642</v>
+        <v>479583</v>
       </c>
       <c r="R50" t="n">
-        <v>6953724</v>
+        <v>6953383</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6093,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122186016</v>
+        <v>122186014</v>
       </c>
       <c r="B51" t="n">
-        <v>5489</v>
+        <v>78393</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6109,21 +6109,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479650</v>
+        <v>479647</v>
       </c>
       <c r="R51" t="n">
-        <v>6953743</v>
+        <v>6953742</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122186014</v>
+        <v>122186015</v>
       </c>
       <c r="B52" t="n">
-        <v>78393</v>
+        <v>78301</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6211,21 +6211,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479647</v>
+        <v>479648</v>
       </c>
       <c r="R52" t="n">
-        <v>6953742</v>
+        <v>6953743</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6297,10 +6297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122186018</v>
+        <v>122185999</v>
       </c>
       <c r="B53" t="n">
-        <v>78682</v>
+        <v>92113</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6313,21 +6313,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479659</v>
+        <v>479600</v>
       </c>
       <c r="R53" t="n">
-        <v>6953756</v>
+        <v>6953419</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5583,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122186010</v>
+        <v>122186016</v>
       </c>
       <c r="B46" t="n">
-        <v>78393</v>
+        <v>5489</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479657</v>
+        <v>479650</v>
       </c>
       <c r="R46" t="n">
-        <v>6953719</v>
+        <v>6953743</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186016</v>
+        <v>122186010</v>
       </c>
       <c r="B47" t="n">
-        <v>5489</v>
+        <v>78393</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479650</v>
+        <v>479657</v>
       </c>
       <c r="R47" t="n">
-        <v>6953743</v>
+        <v>6953719</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -5073,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122186017</v>
+        <v>122186012</v>
       </c>
       <c r="B41" t="n">
-        <v>78393</v>
+        <v>78040</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5089,21 +5089,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479660</v>
+        <v>479642</v>
       </c>
       <c r="R41" t="n">
-        <v>6953756</v>
+        <v>6953724</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5175,10 +5175,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122186004</v>
+        <v>122186002</v>
       </c>
       <c r="B42" t="n">
-        <v>78393</v>
+        <v>78392</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479742</v>
+        <v>479905</v>
       </c>
       <c r="R42" t="n">
-        <v>6953544</v>
+        <v>6953264</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5277,10 +5277,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186011</v>
+        <v>122186010</v>
       </c>
       <c r="B43" t="n">
-        <v>78040</v>
+        <v>78393</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5293,21 +5293,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5320,7 +5320,7 @@
         <v>479657</v>
       </c>
       <c r="R43" t="n">
-        <v>6953720</v>
+        <v>6953719</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122186002</v>
+        <v>122186004</v>
       </c>
       <c r="B44" t="n">
-        <v>78392</v>
+        <v>78393</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479905</v>
+        <v>479742</v>
       </c>
       <c r="R44" t="n">
-        <v>6953264</v>
+        <v>6953544</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122186016</v>
+        <v>122186000</v>
       </c>
       <c r="B46" t="n">
-        <v>5489</v>
+        <v>79765</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5595,25 +5595,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101410</v>
+        <v>6461</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479650</v>
+        <v>479720</v>
       </c>
       <c r="R46" t="n">
-        <v>6953743</v>
+        <v>6953578</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5685,10 +5685,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186010</v>
+        <v>122186015</v>
       </c>
       <c r="B47" t="n">
-        <v>78393</v>
+        <v>78301</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479657</v>
+        <v>479648</v>
       </c>
       <c r="R47" t="n">
-        <v>6953719</v>
+        <v>6953743</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122186012</v>
+        <v>122186016</v>
       </c>
       <c r="B48" t="n">
-        <v>78040</v>
+        <v>5489</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5803,21 +5803,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>101410</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479642</v>
+        <v>479650</v>
       </c>
       <c r="R48" t="n">
-        <v>6953724</v>
+        <v>6953743</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5889,10 +5889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122186000</v>
+        <v>122186017</v>
       </c>
       <c r="B49" t="n">
-        <v>79765</v>
+        <v>78393</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5901,25 +5901,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479720</v>
+        <v>479660</v>
       </c>
       <c r="R49" t="n">
-        <v>6953578</v>
+        <v>6953756</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5991,10 +5991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122185998</v>
+        <v>122186014</v>
       </c>
       <c r="B50" t="n">
-        <v>92125</v>
+        <v>78393</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6003,25 +6003,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479583</v>
+        <v>479647</v>
       </c>
       <c r="R50" t="n">
-        <v>6953383</v>
+        <v>6953742</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6093,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122186014</v>
+        <v>122185998</v>
       </c>
       <c r="B51" t="n">
-        <v>78393</v>
+        <v>92125</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6105,25 +6105,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479647</v>
+        <v>479583</v>
       </c>
       <c r="R51" t="n">
-        <v>6953742</v>
+        <v>6953383</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6163,12 +6163,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6195,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122186015</v>
+        <v>122185999</v>
       </c>
       <c r="B52" t="n">
-        <v>78301</v>
+        <v>92113</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6207,25 +6207,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479648</v>
+        <v>479600</v>
       </c>
       <c r="R52" t="n">
-        <v>6953743</v>
+        <v>6953419</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6265,12 +6265,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6297,10 +6297,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122185999</v>
+        <v>122186011</v>
       </c>
       <c r="B53" t="n">
-        <v>92113</v>
+        <v>78040</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6309,25 +6309,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479600</v>
+        <v>479657</v>
       </c>
       <c r="R53" t="n">
-        <v>6953419</v>
+        <v>6953720</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6397,6 +6397,327 @@
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129294299</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>479756</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6953605</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129294246</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>479755</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6953617</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129294027</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>479675</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6953714</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6718,6 +6718,327 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129304558</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>479696</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6953496</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129304557</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80144</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>479710</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6953558</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129304551</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>479639</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6953558</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Kronfjäll</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -6402,7 +6402,7 @@
         <v>129294299</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>129294246</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>129294027</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>129304558</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>129304557</v>
       </c>
       <c r="B58" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>129304551</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -6402,7 +6402,7 @@
         <v>129294299</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>129294246</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>129294027</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>129304558</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>129304557</v>
       </c>
       <c r="B58" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>129304551</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -6402,7 +6402,7 @@
         <v>129294299</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>129294246</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>129294027</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>129304558</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>129304557</v>
       </c>
       <c r="B58" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>129304551</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -6402,7 +6402,7 @@
         <v>129294299</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>129294246</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>129294027</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>129304558</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>129304557</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>129304551</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -6402,7 +6402,7 @@
         <v>129294299</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>129294246</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>129294027</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>129304558</v>
       </c>
       <c r="B57" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>129304557</v>
       </c>
       <c r="B58" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>129304551</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -6402,7 +6402,7 @@
         <v>129294299</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>129294246</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>129294027</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>129304558</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>129304557</v>
       </c>
       <c r="B58" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>129304551</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -6723,7 +6723,7 @@
         <v>129304558</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>129304557</v>
       </c>
       <c r="B58" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>129304551</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -7044,7 +7044,7 @@
         <v>130185371</v>
       </c>
       <c r="B60" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -7044,7 +7044,7 @@
         <v>130185371</v>
       </c>
       <c r="B60" t="n">
-        <v>79770</v>
+        <v>79773</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -7044,7 +7044,7 @@
         <v>130185371</v>
       </c>
       <c r="B60" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -7044,7 +7044,7 @@
         <v>130185371</v>
       </c>
       <c r="B60" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117940275</v>
+        <v>117943796</v>
       </c>
       <c r="B2" t="n">
-        <v>79073</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Slåttloken, Slåttloken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479803</v>
+        <v>479553</v>
       </c>
       <c r="R2" t="n">
-        <v>6953633</v>
+        <v>6953715</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -761,6 +756,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vid hänsynskrävande surdråg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117941137</v>
+        <v>117938179</v>
       </c>
       <c r="B3" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479903</v>
+        <v>479749</v>
       </c>
       <c r="R3" t="n">
-        <v>6953255</v>
+        <v>6953702</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117941496</v>
+        <v>122186007</v>
       </c>
       <c r="B4" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479807</v>
+        <v>479659</v>
       </c>
       <c r="R4" t="n">
-        <v>6953276</v>
+        <v>6953294</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117938509</v>
+        <v>122186015</v>
       </c>
       <c r="B5" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479758</v>
+        <v>479648</v>
       </c>
       <c r="R5" t="n">
-        <v>6953656</v>
+        <v>6953743</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,62 +1076,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117941282</v>
+        <v>117936812</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479820</v>
+        <v>479671</v>
       </c>
       <c r="R6" t="n">
-        <v>6953242</v>
+        <v>6953744</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,7 +1158,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1168,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117938218</v>
+        <v>122185999</v>
       </c>
       <c r="B7" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,37 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479757</v>
+        <v>479600</v>
       </c>
       <c r="R7" t="n">
-        <v>6953691</v>
+        <v>6953419</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,70 +1280,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117937050</v>
+        <v>122185998</v>
       </c>
       <c r="B8" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479672</v>
+        <v>479583</v>
       </c>
       <c r="R8" t="n">
-        <v>6953743</v>
+        <v>6953383</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,22 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,62 +1377,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117938179</v>
+        <v>117941008</v>
       </c>
       <c r="B9" t="n">
-        <v>78129</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479749</v>
+        <v>479958</v>
       </c>
       <c r="R9" t="n">
-        <v>6953702</v>
+        <v>6953321</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1576,19 +1496,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117943232</v>
+        <v>117941078</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1612,17 +1527,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479604</v>
+        <v>479904</v>
       </c>
       <c r="R10" t="n">
-        <v>6953667</v>
+        <v>6953265</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,7 +1566,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1576,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,62 +1591,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117938245</v>
+        <v>117941941</v>
       </c>
       <c r="B11" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479770</v>
+        <v>479761</v>
       </c>
       <c r="R11" t="n">
-        <v>6953643</v>
+        <v>6953483</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1800,19 +1710,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117941008</v>
+        <v>117942062</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1836,17 +1741,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479958</v>
+        <v>479773</v>
       </c>
       <c r="R12" t="n">
-        <v>6953321</v>
+        <v>6953376</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,7 +1780,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1790,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,31 +1805,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117941941</v>
+        <v>117943232</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1948,14 +1848,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479761</v>
+        <v>479604</v>
       </c>
       <c r="R13" t="n">
-        <v>6953483</v>
+        <v>6953667</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2024,53 +1924,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117942960</v>
+        <v>117943674</v>
       </c>
       <c r="B14" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Slåttloken, Slåttloken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479556</v>
+        <v>479569</v>
       </c>
       <c r="R14" t="n">
-        <v>6953566</v>
+        <v>6953686</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,7 +1994,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2004,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I hänsynskrävande surdråg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,65 +2024,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117937581</v>
+        <v>129294027</v>
       </c>
       <c r="B15" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479671</v>
+        <v>479675</v>
       </c>
       <c r="R15" t="n">
-        <v>6953726</v>
+        <v>6953714</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,22 +2101,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,65 +2131,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117942713</v>
+        <v>129294246</v>
       </c>
       <c r="B16" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479700</v>
+        <v>479755</v>
       </c>
       <c r="R16" t="n">
-        <v>6953611</v>
+        <v>6953617</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,22 +2208,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,65 +2238,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117939942</v>
+        <v>129294299</v>
       </c>
       <c r="B17" t="n">
-        <v>79073</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479815</v>
+        <v>479756</v>
       </c>
       <c r="R17" t="n">
-        <v>6953640</v>
+        <v>6953605</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,22 +2315,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,31 +2345,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117943674</v>
+        <v>129304551</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2508,17 +2388,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttloken (Slåttloken), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479569</v>
+        <v>479639</v>
       </c>
       <c r="R18" t="n">
-        <v>6953686</v>
+        <v>6953558</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,27 +2422,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>I hänsynskrävande surdråg</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,31 +2452,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117941078</v>
+        <v>129304558</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2625,14 +2495,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479904</v>
+        <v>479696</v>
       </c>
       <c r="R19" t="n">
-        <v>6953265</v>
+        <v>6953496</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2659,22 +2529,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,65 +2559,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117937373</v>
+        <v>122186018</v>
       </c>
       <c r="B20" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479671</v>
+        <v>479659</v>
       </c>
       <c r="R20" t="n">
-        <v>6953727</v>
+        <v>6953756</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2771,22 +2636,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,70 +2656,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117938127</v>
+        <v>122186011</v>
       </c>
       <c r="B21" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479712</v>
+        <v>479657</v>
       </c>
       <c r="R21" t="n">
-        <v>6953704</v>
+        <v>6953720</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2888,22 +2733,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,27 +2753,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117941402</v>
+        <v>122186012</v>
       </c>
       <c r="B22" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2946,37 +2776,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479824</v>
+        <v>479642</v>
       </c>
       <c r="R22" t="n">
-        <v>6953250</v>
+        <v>6953724</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,22 +2830,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,62 +2850,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117941433</v>
+        <v>117938245</v>
       </c>
       <c r="B23" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479796</v>
+        <v>479770</v>
       </c>
       <c r="R23" t="n">
-        <v>6953252</v>
+        <v>6953643</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3154,15 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117941367</v>
+        <v>117938509</v>
       </c>
       <c r="B24" t="n">
-        <v>79073</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,34 +2980,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479807</v>
+        <v>479758</v>
       </c>
       <c r="R24" t="n">
-        <v>6953285</v>
+        <v>6953656</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3266,53 +3076,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117937924</v>
+        <v>122186002</v>
       </c>
       <c r="B25" t="n">
-        <v>96801</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479739</v>
+        <v>479905</v>
       </c>
       <c r="R25" t="n">
-        <v>6953704</v>
+        <v>6953264</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3336,22 +3141,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,27 +3161,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117940586</v>
+        <v>122186005</v>
       </c>
       <c r="B26" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3394,37 +3184,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479857</v>
+        <v>479654</v>
       </c>
       <c r="R26" t="n">
-        <v>6953493</v>
+        <v>6953297</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3448,22 +3238,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3478,62 +3258,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117936812</v>
+        <v>117937373</v>
       </c>
       <c r="B27" t="n">
-        <v>90654</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
         <v>479671</v>
       </c>
       <c r="R27" t="n">
-        <v>6953744</v>
+        <v>6953727</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3565,7 +3340,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3575,7 +3350,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,15 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117942314</v>
+        <v>117940586</v>
       </c>
       <c r="B28" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3618,34 +3388,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479741</v>
+        <v>479857</v>
       </c>
       <c r="R28" t="n">
-        <v>6953389</v>
+        <v>6953493</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3677,7 +3447,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3457,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,15 +3484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117938475</v>
+        <v>117938085</v>
       </c>
       <c r="B29" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,37 +3495,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479758</v>
+        <v>479712</v>
       </c>
       <c r="R29" t="n">
-        <v>6953656</v>
+        <v>6953704</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3789,7 +3554,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,7 +3564,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,27 +3579,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117942861</v>
+        <v>117941282</v>
       </c>
       <c r="B30" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,37 +3602,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479638</v>
+        <v>479820</v>
       </c>
       <c r="R30" t="n">
-        <v>6953606</v>
+        <v>6953242</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3901,7 +3661,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3671,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3926,27 +3686,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117938085</v>
+        <v>117942960</v>
       </c>
       <c r="B31" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3974,17 +3729,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479712</v>
+        <v>479556</v>
       </c>
       <c r="R31" t="n">
-        <v>6953704</v>
+        <v>6953566</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4013,7 +3768,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4023,7 +3778,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4038,65 +3793,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117942064</v>
+        <v>129304557</v>
       </c>
       <c r="B32" t="n">
-        <v>97867</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479735</v>
+        <v>479710</v>
       </c>
       <c r="R32" t="n">
-        <v>6953521</v>
+        <v>6953558</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4120,22 +3870,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,27 +3900,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Daniel Kronfjäll</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117939984</v>
+        <v>130184572</v>
       </c>
       <c r="B33" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,37 +3923,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Slåttloken, Slåttloken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479815</v>
+        <v>479548</v>
       </c>
       <c r="R33" t="n">
-        <v>6953640</v>
+        <v>6953680</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4232,22 +3977,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4274,50 +4019,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117938894</v>
+        <v>117941433</v>
       </c>
       <c r="B34" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479776</v>
+        <v>479796</v>
       </c>
       <c r="R34" t="n">
-        <v>6953614</v>
+        <v>6953252</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4386,15 +4126,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117941709</v>
+        <v>122186000</v>
       </c>
       <c r="B35" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4402,42 +4137,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479783</v>
+        <v>479720</v>
       </c>
       <c r="R35" t="n">
-        <v>6953379</v>
+        <v>6953578</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4461,22 +4191,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4491,27 +4211,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117936521</v>
+        <v>117940785</v>
       </c>
       <c r="B36" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4519,37 +4234,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479658</v>
+        <v>479909</v>
       </c>
       <c r="R36" t="n">
-        <v>6953757</v>
+        <v>6953394</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4578,7 +4298,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4588,7 +4308,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4603,27 +4323,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117942062</v>
+        <v>117942027</v>
       </c>
       <c r="B37" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4631,37 +4346,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479773</v>
+        <v>479728</v>
       </c>
       <c r="R37" t="n">
-        <v>6953376</v>
+        <v>6953486</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4690,7 +4410,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4700,7 +4420,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4715,65 +4435,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117941840</v>
+        <v>117937050</v>
       </c>
       <c r="B38" t="n">
-        <v>5480</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101410</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479804</v>
+        <v>479672</v>
       </c>
       <c r="R38" t="n">
-        <v>6953380</v>
+        <v>6953743</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4802,7 +4522,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4812,7 +4532,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4827,70 +4547,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117940785</v>
+        <v>117938127</v>
       </c>
       <c r="B39" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken (Trätmyrbäcken), Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479909</v>
+        <v>479712</v>
       </c>
       <c r="R39" t="n">
-        <v>6953394</v>
+        <v>6953704</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4919,7 +4634,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4929,7 +4644,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4944,67 +4659,62 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117942027</v>
+        <v>117941709</v>
       </c>
       <c r="B40" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Björnberget (Björnberget), Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479728</v>
+        <v>479783</v>
       </c>
       <c r="R40" t="n">
-        <v>6953486</v>
+        <v>6953379</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5073,15 +4783,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122186012</v>
+        <v>117941840</v>
       </c>
       <c r="B41" t="n">
-        <v>78040</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5089,37 +4794,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>101410</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479642</v>
+        <v>479804</v>
       </c>
       <c r="R41" t="n">
-        <v>6953724</v>
+        <v>6953380</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5143,12 +4848,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5163,27 +4878,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122186002</v>
+        <v>122186016</v>
       </c>
       <c r="B42" t="n">
-        <v>78392</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5191,21 +4901,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>101410</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479905</v>
+        <v>479650</v>
       </c>
       <c r="R42" t="n">
-        <v>6953264</v>
+        <v>6953743</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5245,12 +4955,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5277,15 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122186010</v>
+        <v>122186008</v>
       </c>
       <c r="B43" t="n">
-        <v>78393</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5293,21 +4998,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5317,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479657</v>
+        <v>479580</v>
       </c>
       <c r="R43" t="n">
-        <v>6953719</v>
+        <v>6953297</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5347,12 +5052,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,53 +5084,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122186004</v>
+        <v>117937924</v>
       </c>
       <c r="B44" t="n">
-        <v>78393</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479742</v>
+        <v>479739</v>
       </c>
       <c r="R44" t="n">
-        <v>6953544</v>
+        <v>6953704</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5449,12 +5149,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5469,27 +5179,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122186018</v>
+        <v>117942064</v>
       </c>
       <c r="B45" t="n">
-        <v>78682</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5497,37 +5202,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6434</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479659</v>
+        <v>479735</v>
       </c>
       <c r="R45" t="n">
-        <v>6953756</v>
+        <v>6953521</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5551,12 +5256,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5571,65 +5286,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122186000</v>
+        <v>117936521</v>
       </c>
       <c r="B46" t="n">
-        <v>79765</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479720</v>
+        <v>479658</v>
       </c>
       <c r="R46" t="n">
-        <v>6953578</v>
+        <v>6953757</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5653,12 +5363,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5673,27 +5393,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122186015</v>
+        <v>117937581</v>
       </c>
       <c r="B47" t="n">
-        <v>78301</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,37 +5416,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479648</v>
+        <v>479671</v>
       </c>
       <c r="R47" t="n">
-        <v>6953743</v>
+        <v>6953726</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5755,12 +5470,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5775,27 +5500,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122186016</v>
+        <v>117938218</v>
       </c>
       <c r="B48" t="n">
-        <v>5489</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5803,37 +5523,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479650</v>
+        <v>479757</v>
       </c>
       <c r="R48" t="n">
-        <v>6953743</v>
+        <v>6953691</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5857,12 +5577,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5877,27 +5607,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122186017</v>
+        <v>117938475</v>
       </c>
       <c r="B49" t="n">
-        <v>78393</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5925,17 +5650,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479660</v>
+        <v>479758</v>
       </c>
       <c r="R49" t="n">
-        <v>6953756</v>
+        <v>6953656</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5959,12 +5684,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5979,27 +5714,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122186014</v>
+        <v>117938894</v>
       </c>
       <c r="B50" t="n">
-        <v>78393</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,17 +5757,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479647</v>
+        <v>479776</v>
       </c>
       <c r="R50" t="n">
-        <v>6953742</v>
+        <v>6953614</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6061,12 +5791,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6081,65 +5821,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122185998</v>
+        <v>117939984</v>
       </c>
       <c r="B51" t="n">
-        <v>92125</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479583</v>
+        <v>479815</v>
       </c>
       <c r="R51" t="n">
-        <v>6953383</v>
+        <v>6953640</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6163,12 +5898,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6183,65 +5928,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122185999</v>
+        <v>117941137</v>
       </c>
       <c r="B52" t="n">
-        <v>92113</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479600</v>
+        <v>479903</v>
       </c>
       <c r="R52" t="n">
-        <v>6953419</v>
+        <v>6953255</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6265,12 +6005,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6285,27 +6035,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122186011</v>
+        <v>117941402</v>
       </c>
       <c r="B53" t="n">
-        <v>78040</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6313,37 +6058,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479657</v>
+        <v>479824</v>
       </c>
       <c r="R53" t="n">
-        <v>6953720</v>
+        <v>6953250</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6367,12 +6112,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6387,22 +6142,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129294299</v>
+        <v>117941496</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79085</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6410,37 +6165,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479756</v>
+        <v>479807</v>
       </c>
       <c r="R54" t="n">
-        <v>6953605</v>
+        <v>6953276</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6464,22 +6219,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6494,22 +6249,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129294246</v>
+        <v>117942713</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6517,21 +6272,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6541,13 +6296,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479755</v>
+        <v>479700</v>
       </c>
       <c r="R55" t="n">
-        <v>6953617</v>
+        <v>6953611</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6571,22 +6326,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6601,22 +6356,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129294027</v>
+        <v>117942861</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6624,37 +6379,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
+          <t>Björnberget, Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479675</v>
+        <v>479638</v>
       </c>
       <c r="R56" t="n">
-        <v>6953714</v>
+        <v>6953606</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6678,22 +6433,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6708,22 +6463,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129304558</v>
+        <v>122186004</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79085</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6731,37 +6486,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479696</v>
+        <v>479742</v>
       </c>
       <c r="R57" t="n">
-        <v>6953496</v>
+        <v>6953544</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6785,22 +6540,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6815,22 +6560,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129304557</v>
+        <v>122186006</v>
       </c>
       <c r="B58" t="n">
-        <v>80186</v>
+        <v>79085</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6838,37 +6583,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479710</v>
+        <v>479653</v>
       </c>
       <c r="R58" t="n">
-        <v>6953558</v>
+        <v>6953297</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6892,22 +6637,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6922,22 +6657,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129304551</v>
+        <v>122186010</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>79085</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6945,37 +6680,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>479639</v>
+        <v>479657</v>
       </c>
       <c r="R59" t="n">
-        <v>6953558</v>
+        <v>6953720</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6999,22 +6734,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7029,22 +6754,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Kronfjäll</t>
+          <t>Martin Berg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130185371</v>
+        <v>122186014</v>
       </c>
       <c r="B60" t="n">
-        <v>79801</v>
+        <v>79085</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7052,37 +6777,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>479630</v>
+        <v>479647</v>
       </c>
       <c r="R60" t="n">
-        <v>6953743</v>
+        <v>6953742</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7106,22 +6831,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7136,15 +6851,540 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122186017</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>479660</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6953756</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>117939942</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>479815</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6953640</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
           <t>Erik Wilhelmsson</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
+      <c r="AX62" t="inlineStr">
         <is>
           <t>Erik Wilhelmsson</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>117940275</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>479803</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6953633</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>117941367</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>479807</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6953285</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130185371</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Trätmyrbäcken, Trätmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>479630</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6953743</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18411-2024 artfynd.xlsx
+++ b/artfynd/A 18411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117943796</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938179</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186007</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186015</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117936812</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122185999</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122185998</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941078</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941941</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942062</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1921,6 +1981,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117943232</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117943674</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294027</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2247,6 +2322,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294246</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2354,6 +2434,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294299</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2461,6 +2546,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129304551</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2568,6 +2658,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129304558</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186018</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2762,6 +2862,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186011</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2859,6 +2964,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186012</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2966,6 +3076,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938245</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3073,6 +3188,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938509</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3170,6 +3290,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186002</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3267,6 +3392,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186005</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3374,6 +3504,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937373</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3481,6 +3616,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940586</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3588,6 +3728,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938085</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3695,6 +3840,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941282</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3802,6 +3952,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942960</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3909,6 +4064,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129304557</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4016,6 +4176,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184572</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4123,6 +4288,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941433</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4220,6 +4390,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186000</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4332,6 +4507,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940785</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4444,6 +4624,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942027</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4556,6 +4741,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937050</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4668,6 +4858,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938127</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4780,6 +4975,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941709</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4887,6 +5087,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941840</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4984,6 +5189,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186016</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5081,6 +5291,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186008</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5188,6 +5403,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937924</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5295,6 +5515,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942064</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5402,6 +5627,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117936521</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5509,6 +5739,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937581</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5616,6 +5851,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938218</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5723,6 +5963,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938475</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5830,6 +6075,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938894</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5937,6 +6187,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939984</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6044,6 +6299,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941137</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6151,6 +6411,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941402</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6258,6 +6523,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941496</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6365,6 +6635,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942713</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6472,6 +6747,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942861</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6569,6 +6849,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186004</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6666,6 +6951,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186006</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6763,6 +7053,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186010</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6860,6 +7155,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186014</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6957,6 +7257,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122186017</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7064,6 +7369,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939942</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7171,6 +7481,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940275</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7278,6 +7593,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941367</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7385,8 +7705,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130185371</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>